--- a/questionnaire_templates/024_one_on_one_meeting_focus_sheet_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/024_one_on_one_meeting_focus_sheet_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the meeting topic</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Meeting Topic</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the meeting topic</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>meeting_date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select the meeting date</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>meeting_time</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Meeting Time</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select the meeting time</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,107 +601,127 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>meeting_location</t>
+          <t>meeting_outcomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>meeting_location</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Meeting Outcomes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please describe the meeting outcomes</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>meeting_notes</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>meeting_notes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Next Steps</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please describe the next steps</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>meeting_outcomes</t>
+          <t>next_meeting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>meeting_outcomes</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Next Meeting</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select the next meeting date</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>minimalism</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Importance of Minimalism</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select how important is minimalism in this meeting</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>meeting_outcomes_follow_up</t>
+          <t>meeting_notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>meeting_outcomes_follow_up</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Meeting Notes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe the meeting notes</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>next_meeting</t>
+          <t>minimalism2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>next_meeting</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Minimalism Relevant</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Do you think minimalism is relevant in this meeting</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>minimalism</t>
+          <t>minimalism3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>minimalism</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Minimalism Importance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select the importance of minimalism in this meeting</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>minimalism2</t>
+          <t>next_meeting2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>minimalism2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Next Meeting2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select the next meeting date</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,297 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>minimalism2</t>
+          <t>minimalism4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>minimalism2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Minimalism Follow-up</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please describe the minimalism follow-up</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>minimalism2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>minimalism2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>minimalism3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>minimalism4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>minimalism4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>minimalism5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>minimalism5</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>minimalism6</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>minimalism6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>minimalism7</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>minimalism7</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,187 +875,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>minimalism3_choices</t>
+          <t>minimalism_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>minimalism3_choices</t>
+          <t>minimalism_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>minimalism3_choices</t>
+          <t>minimalism_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>minimalism3_choices</t>
+          <t>minimalism2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_d</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>minimalism3_choices</t>
+          <t>minimalism2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_e</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option E</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>minimalism3_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>option_f</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Option F</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>minimalism3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_g</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option G</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>minimalism3_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option_h</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Option H</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>minimalism3_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option_i</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Option I</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>minimalism7_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>minimalism7_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
